--- a/tame_output/ON/bt/strategyON_20240111.xlsx
+++ b/tame_output/ON/bt/strategyON_20240111.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,16 +610,16 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1835</v>
+        <v>1836</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-01-09</t>
+          <t>2024-01-10</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>9.8%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>78.4%</t>
+          <t>79.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1835</v>
+        <v>1836</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-01-09</t>
+          <t>2024-01-10</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>64.6%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>4.1%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1835</v>
+        <v>1836</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-01-09</t>
+          <t>2024-01-10</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>54.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>1.0%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>101.4%</t>
+          <t>102.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1835</v>
+        <v>1836</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-01-09</t>
+          <t>2024-01-10</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>30.9%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>96.5%</t>
+          <t>97.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>40.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>4.5%</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1835</v>
+        <v>1836</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-01-09</t>
+          <t>2024-01-10</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-155.7%</t>
+          <t>-155.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>130.5%</t>
+          <t>132.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1835</v>
+        <v>1836</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-01-09</t>
+          <t>2024-01-10</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>124.2%</t>
+          <t>125.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>37.1%</t>
+          <t>37.2%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>3.6%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1838"/>
+  <dimension ref="A1:G1839"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43819,7 +43819,7 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.370373729152028</v>
+        <v>3.367379938511406</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
@@ -43835,6 +43835,29 @@
       </c>
       <c r="G1838" t="n">
         <v>4.461574820915785</v>
+      </c>
+    </row>
+    <row r="1839">
+      <c r="A1839" s="2" t="n">
+        <v>45301</v>
+      </c>
+      <c r="B1839" t="n">
+        <v>3.378821167884937</v>
+      </c>
+      <c r="C1839" t="n">
+        <v>3.157511256610484</v>
+      </c>
+      <c r="D1839" t="n">
+        <v>1.625886394469037</v>
+      </c>
+      <c r="E1839" t="n">
+        <v>3.807509390084352</v>
+      </c>
+      <c r="F1839" t="n">
+        <v>2.231674414671404</v>
+      </c>
+      <c r="G1839" t="n">
+        <v>4.496515905413327</v>
       </c>
     </row>
   </sheetData>
